--- a/artfynd/A 25524-2026 artfynd.xlsx
+++ b/artfynd/A 25524-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119126377</v>
+        <v>128592352</v>
       </c>
       <c r="B2" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572958</v>
+        <v>572961</v>
       </c>
       <c r="R2" t="n">
-        <v>6784136</v>
+        <v>6784108</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +776,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,37 +794,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119126355</v>
+        <v>127503624</v>
       </c>
       <c r="B3" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,13 +827,13 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -882,12 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +895,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127503624</v>
+        <v>126373197</v>
       </c>
       <c r="B4" t="n">
-        <v>57956</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,46 +924,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söråsens skog, Hls</t>
+          <t>Söråsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572961</v>
+        <v>573007</v>
       </c>
       <c r="R4" t="n">
-        <v>6784108</v>
+        <v>6784115</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,22 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,75 +996,68 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128592352</v>
+        <v>126373190</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söråsens skog, Hls</t>
+          <t>Söråsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572961</v>
+        <v>573007</v>
       </c>
       <c r="R5" t="n">
-        <v>6784108</v>
+        <v>6784115</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,22 +1084,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,33 +1098,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118036851</v>
+        <v>126373232</v>
       </c>
       <c r="B6" t="n">
-        <v>97766</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,30 +1128,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1201,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573148</v>
+        <v>573007</v>
       </c>
       <c r="R6" t="n">
-        <v>6784152</v>
+        <v>6784115</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,22 +1186,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,50 +1207,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118036809</v>
+        <v>119126355</v>
       </c>
       <c r="B7" t="n">
-        <v>97766</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1318,17 +1262,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söråsen, Hls</t>
+          <t>Söråsens skog, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573141</v>
+        <v>572961</v>
       </c>
       <c r="R7" t="n">
-        <v>6784172</v>
+        <v>6784108</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,22 +1296,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,65 +1329,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118036763</v>
+        <v>119126377</v>
       </c>
       <c r="B8" t="n">
-        <v>97867</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söråsen, Hls</t>
+          <t>Söråsens skog, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573147</v>
+        <v>572958</v>
       </c>
       <c r="R8" t="n">
-        <v>6784180</v>
+        <v>6784136</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1477,22 +1406,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,6 +1446,460 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118036763</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>573147</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6784180</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126373202</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>573007</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6784115</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Lindholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Lindholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118036809</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>573141</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6784172</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118036851</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>573148</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6784152</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25524-2026 artfynd.xlsx
+++ b/artfynd/A 25524-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126373190</v>
+        <v>134697879</v>
       </c>
       <c r="B5" t="n">
-        <v>99142</v>
+        <v>99112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573007</v>
+        <v>572974</v>
       </c>
       <c r="R5" t="n">
-        <v>6784115</v>
+        <v>6784099</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,12 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,29 +1108,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Lindholm</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Lindholm</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126373232</v>
+        <v>126373190</v>
       </c>
       <c r="B6" t="n">
-        <v>99153</v>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1219,57 +1228,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119126355</v>
+        <v>126373232</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>99153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söråsens skog, Hls</t>
+          <t>Söråsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572961</v>
+        <v>573007</v>
       </c>
       <c r="R7" t="n">
-        <v>6784108</v>
+        <v>6784115</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,19 +1318,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119126377</v>
+        <v>119126355</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1359,7 +1360,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1376,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572958</v>
+        <v>572961</v>
       </c>
       <c r="R8" t="n">
-        <v>6784136</v>
+        <v>6784108</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,19 +1410,9 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,60 +1440,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118036763</v>
+        <v>119126377</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söråsen, Hls</t>
+          <t>Söråsens skog, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573147</v>
+        <v>572958</v>
       </c>
       <c r="R9" t="n">
-        <v>6784180</v>
+        <v>6784136</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,22 +1517,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,52 +1560,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126373202</v>
+        <v>134697698</v>
       </c>
       <c r="B10" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söråsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573007</v>
+        <v>572979</v>
       </c>
       <c r="R10" t="n">
-        <v>6784115</v>
+        <v>6784122</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,12 +1637,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,29 +1661,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Lindholm</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Lindholm</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118036809</v>
+        <v>134700796</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>98063</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,45 +1690,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söråsen, Hls</t>
+          <t>Östansjöbor, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573141</v>
+        <v>573244</v>
       </c>
       <c r="R11" t="n">
-        <v>6784172</v>
+        <v>6784235</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,22 +1748,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,29 +1772,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118036851</v>
+        <v>118036763</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,28 +1801,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1830,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573148</v>
+        <v>573147</v>
       </c>
       <c r="R12" t="n">
-        <v>6784152</v>
+        <v>6784180</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1865,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1882,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,6 +1907,340 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126373202</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>573007</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6784115</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mattias Lindholm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mattias Lindholm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118036809</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>573141</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6784172</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118036851</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>573148</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6784152</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25524-2026 artfynd.xlsx
+++ b/artfynd/A 25524-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128592352</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127503624</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126373197</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134697879</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126373190</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126373232</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119126355</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119126377</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134697698</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134700796</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1907,6 +1962,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118036763</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2009,6 +2069,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126373202</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2125,6 +2190,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118036809</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2241,8 +2311,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118036851</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>